--- a/artfynd/A 8319-2026 artfynd.xlsx
+++ b/artfynd/A 8319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133087959</v>
+        <v>117760790</v>
       </c>
       <c r="B2" t="n">
-        <v>101348</v>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467112</v>
+        <v>467162</v>
       </c>
       <c r="R2" t="n">
-        <v>6968725</v>
+        <v>6968722</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133088092</v>
+        <v>133087959</v>
       </c>
       <c r="B3" t="n">
-        <v>101348</v>
+        <v>101403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467128</v>
+        <v>467112</v>
       </c>
       <c r="R3" t="n">
-        <v>6968710</v>
+        <v>6968725</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133088092</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granmo, Granmo, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467128</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6968710</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8319-2026 artfynd.xlsx
+++ b/artfynd/A 8319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117760790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133087959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133088092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>